--- a/src/locales/moneyGone.xlsx
+++ b/src/locales/moneyGone.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="工作表1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="moneygone" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="475">
   <si>
     <t>key</t>
   </si>
@@ -28,19 +28,1414 @@
     <t>ja-JP</t>
   </si>
   <si>
-    <t>LC_TEST</t>
-  </si>
-  <si>
-    <t>測試</t>
-  </si>
-  <si>
-    <t>測試 cn</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>test jp</t>
+    <t>LC_LOBBY</t>
+  </si>
+  <si>
+    <t>大廳</t>
+  </si>
+  <si>
+    <t>大厅</t>
+  </si>
+  <si>
+    <t>Lobby</t>
+  </si>
+  <si>
+    <t>ロビー</t>
+  </si>
+  <si>
+    <t>LC_OVERVIEW</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>LC_VIEW_CHART</t>
+  </si>
+  <si>
+    <t>查看圖表</t>
+  </si>
+  <si>
+    <t>查看图表</t>
+  </si>
+  <si>
+    <t>View Chart</t>
+  </si>
+  <si>
+    <t>チャートを見る</t>
+  </si>
+  <si>
+    <t>LC_SPEND_TODAY</t>
+  </si>
+  <si>
+    <t>今日花費</t>
+  </si>
+  <si>
+    <t>今日花费</t>
+  </si>
+  <si>
+    <t>Today's Spending</t>
+  </si>
+  <si>
+    <t>今日の支出</t>
+  </si>
+  <si>
+    <t>LC_SPEND_MONTH</t>
+  </si>
+  <si>
+    <t>本月花費</t>
+  </si>
+  <si>
+    <t>本月花费</t>
+  </si>
+  <si>
+    <t>Monthly Spending</t>
+  </si>
+  <si>
+    <t>今月の支出</t>
+  </si>
+  <si>
+    <t>LC_OVER</t>
+  </si>
+  <si>
+    <t>剩餘</t>
+  </si>
+  <si>
+    <t>剩余</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>残り</t>
+  </si>
+  <si>
+    <t>LC_CATEGORY</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>カテゴリ</t>
+  </si>
+  <si>
+    <t>LC_EDIT_CATEGORY</t>
+  </si>
+  <si>
+    <t>編輯分類</t>
+  </si>
+  <si>
+    <t>编辑分类</t>
+  </si>
+  <si>
+    <t>Edit Category</t>
+  </si>
+  <si>
+    <t>カテゴリを編集</t>
+  </si>
+  <si>
+    <t>LC_VIEW_RECORD</t>
+  </si>
+  <si>
+    <t>查看紀錄</t>
+  </si>
+  <si>
+    <t>查看记录</t>
+  </si>
+  <si>
+    <t>View Record</t>
+  </si>
+  <si>
+    <t>記録を見る</t>
+  </si>
+  <si>
+    <t>LC_NO_SPEND</t>
+  </si>
+  <si>
+    <t>今天還沒有錢錢犧牲</t>
+  </si>
+  <si>
+    <t>今天还没有钱钱牺牲</t>
+  </si>
+  <si>
+    <t>No spending today</t>
+  </si>
+  <si>
+    <t>今日の支出はまだありません</t>
+  </si>
+  <si>
+    <t>LC_HOME</t>
+  </si>
+  <si>
+    <t>首頁</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>ホーム</t>
+  </si>
+  <si>
+    <t>LC_RECORD</t>
+  </si>
+  <si>
+    <t>紀錄</t>
+  </si>
+  <si>
+    <t>记录</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>記録</t>
+  </si>
+  <si>
+    <t>LC_CHART</t>
+  </si>
+  <si>
+    <t>圖表</t>
+  </si>
+  <si>
+    <t>图表</t>
+  </si>
+  <si>
+    <t>Chart</t>
+  </si>
+  <si>
+    <t>チャート</t>
+  </si>
+  <si>
+    <t>LC_SETTING</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>LC_SELECT_CATEGORY</t>
+  </si>
+  <si>
+    <t>選擇分類</t>
+  </si>
+  <si>
+    <t>选择分类</t>
+  </si>
+  <si>
+    <t>Select Category</t>
+  </si>
+  <si>
+    <t>カテゴリを選択</t>
+  </si>
+  <si>
+    <t>LC_CATEGORY_EMPTY</t>
+  </si>
+  <si>
+    <t>目前沒有任何分類</t>
+  </si>
+  <si>
+    <t>目前没有任何分类</t>
+  </si>
+  <si>
+    <t>No categories available</t>
+  </si>
+  <si>
+    <t>現在カテゴリがありません</t>
+  </si>
+  <si>
+    <t>LC_TO_ADD</t>
+  </si>
+  <si>
+    <t>前往新增</t>
+  </si>
+  <si>
+    <t>Go to add</t>
+  </si>
+  <si>
+    <t>追加へ</t>
+  </si>
+  <si>
+    <t>LC_ADD</t>
+  </si>
+  <si>
+    <t>新增</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>追加</t>
+  </si>
+  <si>
+    <t>LC_DATE</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>日付</t>
+  </si>
+  <si>
+    <t>LC_NAME</t>
+  </si>
+  <si>
+    <t>名稱</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>LC_TIPS_NAME</t>
+  </si>
+  <si>
+    <t>請輸入名稱</t>
+  </si>
+  <si>
+    <t>请输入名称</t>
+  </si>
+  <si>
+    <t>Please enter a name</t>
+  </si>
+  <si>
+    <t>名前を入力してください</t>
+  </si>
+  <si>
+    <t>LC_AMOUNT</t>
+  </si>
+  <si>
+    <t>金額</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>LC_TIPS_AMOUNT</t>
+  </si>
+  <si>
+    <t>請輸入金額</t>
+  </si>
+  <si>
+    <t>请输入金额</t>
+  </si>
+  <si>
+    <t>Please enter an amount</t>
+  </si>
+  <si>
+    <t>金額を入力してください</t>
+  </si>
+  <si>
+    <t>LC_NOTE</t>
+  </si>
+  <si>
+    <t>備註</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>LC_TIPS_NOTE</t>
+  </si>
+  <si>
+    <t>請輸入備註</t>
+  </si>
+  <si>
+    <t>请输入备注</t>
+  </si>
+  <si>
+    <t>Please enter a note</t>
+  </si>
+  <si>
+    <t>備考を入力してください</t>
+  </si>
+  <si>
+    <t>LC_TIPS_RECORD</t>
+  </si>
+  <si>
+    <t>請輸入分類或名稱</t>
+  </si>
+  <si>
+    <t>请输入分类或名称</t>
+  </si>
+  <si>
+    <t>Please enter a category or name</t>
+  </si>
+  <si>
+    <t>カテゴリまたは名前を入力してください</t>
+  </si>
+  <si>
+    <t>LC_SPEND_DETAILS</t>
+  </si>
+  <si>
+    <t>花費詳情</t>
+  </si>
+  <si>
+    <t>花费详情</t>
+  </si>
+  <si>
+    <t>Spending Details</t>
+  </si>
+  <si>
+    <t>支出の詳細</t>
+  </si>
+  <si>
+    <t>LC_RECORD_EMPTY</t>
+  </si>
+  <si>
+    <t>這個月還沒有消費</t>
+  </si>
+  <si>
+    <t>这个月还没有消费</t>
+  </si>
+  <si>
+    <t>No spending this month</t>
+  </si>
+  <si>
+    <t>今月はまだ支出がありません</t>
+  </si>
+  <si>
+    <t>LC_BAR_CHART</t>
+  </si>
+  <si>
+    <t>長條圖</t>
+  </si>
+  <si>
+    <t>长条图</t>
+  </si>
+  <si>
+    <t>Bar Chart</t>
+  </si>
+  <si>
+    <t>棒グラフ</t>
+  </si>
+  <si>
+    <t>LC_DONUT_CHART</t>
+  </si>
+  <si>
+    <t>環形圖</t>
+  </si>
+  <si>
+    <t>环形图</t>
+  </si>
+  <si>
+    <t>Donut Chart</t>
+  </si>
+  <si>
+    <t>ドーナツチャート</t>
+  </si>
+  <si>
+    <t>LC_MONTH_REPORT</t>
+  </si>
+  <si>
+    <t>月報表</t>
+  </si>
+  <si>
+    <t>月报表</t>
+  </si>
+  <si>
+    <t>Monthly Report</t>
+  </si>
+  <si>
+    <t>月次レポート</t>
+  </si>
+  <si>
+    <t>LC_YEAR_REPORT</t>
+  </si>
+  <si>
+    <t>年報表</t>
+  </si>
+  <si>
+    <t>年报表</t>
+  </si>
+  <si>
+    <t>Yearly Report</t>
+  </si>
+  <si>
+    <t>年次レポート</t>
+  </si>
+  <si>
+    <t>LC_FIRST_HALF</t>
+  </si>
+  <si>
+    <t>上半月</t>
+  </si>
+  <si>
+    <t>First Half of the Month</t>
+  </si>
+  <si>
+    <t>月の前半</t>
+  </si>
+  <si>
+    <t>LC_SECOND_HALF</t>
+  </si>
+  <si>
+    <t>下半月</t>
+  </si>
+  <si>
+    <t>Second Half of the Month</t>
+  </si>
+  <si>
+    <t>月の後半</t>
+  </si>
+  <si>
+    <t>LC_MONTH_TOP</t>
+  </si>
+  <si>
+    <t>本月 TOP 5 花費</t>
+  </si>
+  <si>
+    <t>本月 TOP 5 花费</t>
+  </si>
+  <si>
+    <t>Top 5 Spendings This Month</t>
+  </si>
+  <si>
+    <t>今月のトップ5支出</t>
+  </si>
+  <si>
+    <t>LC_YEAR_TOP</t>
+  </si>
+  <si>
+    <t>年度 TOP 5 花費</t>
+  </si>
+  <si>
+    <t>年度 TOP 5 花费</t>
+  </si>
+  <si>
+    <t>Top 5 Spendings This Year</t>
+  </si>
+  <si>
+    <t>今年のトップ5支出</t>
+  </si>
+  <si>
+    <t>LC_MONTH_TOTAL</t>
+  </si>
+  <si>
+    <t>本月總和</t>
+  </si>
+  <si>
+    <t>本月总和</t>
+  </si>
+  <si>
+    <t>Monthly total</t>
+  </si>
+  <si>
+    <t>今月の合計</t>
+  </si>
+  <si>
+    <t>LC_YEAR_TOTAL</t>
+  </si>
+  <si>
+    <t>年度總和</t>
+  </si>
+  <si>
+    <t>年度总和</t>
+  </si>
+  <si>
+    <t>Yearly total</t>
+  </si>
+  <si>
+    <t>年間の合計</t>
+  </si>
+  <si>
+    <t>LC_CATEGORY_DETAILS</t>
+  </si>
+  <si>
+    <t>分類明細</t>
+  </si>
+  <si>
+    <t>分类明细</t>
+  </si>
+  <si>
+    <t>Category Details</t>
+  </si>
+  <si>
+    <t>カテゴリの詳細</t>
+  </si>
+  <si>
+    <t>LC_CHART_EMPTY</t>
+  </si>
+  <si>
+    <t>此區間沒有任何消費</t>
+  </si>
+  <si>
+    <t>此区间没有任何消费</t>
+  </si>
+  <si>
+    <t>No spending in this period</t>
+  </si>
+  <si>
+    <t>この期間の支出はありません</t>
+  </si>
+  <si>
+    <t>LC_ACCOUNT_NAME</t>
+  </si>
+  <si>
+    <t>暱稱</t>
+  </si>
+  <si>
+    <t>昵称</t>
+  </si>
+  <si>
+    <t>Nickname</t>
+  </si>
+  <si>
+    <t>ニックネーム</t>
+  </si>
+  <si>
+    <t>LC_EDIT_ACCOUNT_NAME</t>
+  </si>
+  <si>
+    <t>編輯暱稱</t>
+  </si>
+  <si>
+    <t>编辑昵称</t>
+  </si>
+  <si>
+    <t>Edit Nickname</t>
+  </si>
+  <si>
+    <t>ニックネームを編集</t>
+  </si>
+  <si>
+    <t>LC_TIPS_ACCOUNT_NAME</t>
+  </si>
+  <si>
+    <t>請輸入暱稱</t>
+  </si>
+  <si>
+    <t>请输入昵称</t>
+  </si>
+  <si>
+    <t>Please enter a nickname</t>
+  </si>
+  <si>
+    <t>ニックネームを入力してください</t>
+  </si>
+  <si>
+    <t>LC_BUDGET</t>
+  </si>
+  <si>
+    <t>預算</t>
+  </si>
+  <si>
+    <t>预算</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>予算</t>
+  </si>
+  <si>
+    <t>LC_EDIT_BUDGET</t>
+  </si>
+  <si>
+    <t>編輯預算</t>
+  </si>
+  <si>
+    <t>编辑预算</t>
+  </si>
+  <si>
+    <t>Edit Budget</t>
+  </si>
+  <si>
+    <t>予算を編集</t>
+  </si>
+  <si>
+    <t>LC_BUDGET_TIPS</t>
+  </si>
+  <si>
+    <t>請輸入預算</t>
+  </si>
+  <si>
+    <t>请输入预算</t>
+  </si>
+  <si>
+    <t>Please enter a budget</t>
+  </si>
+  <si>
+    <t>予算を入力してください</t>
+  </si>
+  <si>
+    <t>LC_LANG</t>
+  </si>
+  <si>
+    <t>語系</t>
+  </si>
+  <si>
+    <t>语系</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>言語</t>
+  </si>
+  <si>
+    <t>LC_EDIT_LANG</t>
+  </si>
+  <si>
+    <t>修改語系</t>
+  </si>
+  <si>
+    <t>修改语系</t>
+  </si>
+  <si>
+    <t>Change Language</t>
+  </si>
+  <si>
+    <t>言語を変更</t>
+  </si>
+  <si>
+    <t>LC_LOGOUT</t>
+  </si>
+  <si>
+    <t>登出</t>
+  </si>
+  <si>
+    <t>Logout</t>
+  </si>
+  <si>
+    <t>ログアウト</t>
+  </si>
+  <si>
+    <t>LC_ITEMS</t>
+  </si>
+  <si>
+    <t>{num} 個項目</t>
+  </si>
+  <si>
+    <t>{num} 个项目</t>
+  </si>
+  <si>
+    <t>{num} items</t>
+  </si>
+  <si>
+    <t>{num} 個の項目</t>
+  </si>
+  <si>
+    <t>LC_ADD_CATEGORY</t>
+  </si>
+  <si>
+    <t>新增分類</t>
+  </si>
+  <si>
+    <t>新增分类</t>
+  </si>
+  <si>
+    <t>Add Category</t>
+  </si>
+  <si>
+    <t>カテゴリを追加</t>
+  </si>
+  <si>
+    <t>LC_COLOR</t>
+  </si>
+  <si>
+    <t>顏色</t>
+  </si>
+  <si>
+    <t>颜色</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>色</t>
+  </si>
+  <si>
+    <t>LC_SELECT_IMG</t>
+  </si>
+  <si>
+    <t>選擇圖示</t>
+  </si>
+  <si>
+    <t>选择图示</t>
+  </si>
+  <si>
+    <t>Select Icon</t>
+  </si>
+  <si>
+    <t>アイコンを選択</t>
+  </si>
+  <si>
+    <t>LC_IMG_UPLOAD</t>
+  </si>
+  <si>
+    <t>上傳圖片</t>
+  </si>
+  <si>
+    <t>上传图片</t>
+  </si>
+  <si>
+    <t>Upload Image</t>
+  </si>
+  <si>
+    <t>画像をアップロード</t>
+  </si>
+  <si>
+    <t>LC_DELETE_IMG</t>
+  </si>
+  <si>
+    <t>刪除圖片</t>
+  </si>
+  <si>
+    <t>删除图片</t>
+  </si>
+  <si>
+    <t>Delete image</t>
+  </si>
+  <si>
+    <t>画像を削除</t>
+  </si>
+  <si>
+    <t>LC_EDIT_SHORTCUTS</t>
+  </si>
+  <si>
+    <t>編輯子項目</t>
+  </si>
+  <si>
+    <t>编辑子项目</t>
+  </si>
+  <si>
+    <t>Edit Subitems</t>
+  </si>
+  <si>
+    <t>サブ項目を編集</t>
+  </si>
+  <si>
+    <t>LC_SHORTCUTS_EMPTY</t>
+  </si>
+  <si>
+    <t>目前沒有任何子項目</t>
+  </si>
+  <si>
+    <t>目前没有任何子项目</t>
+  </si>
+  <si>
+    <t>No subitems currently</t>
+  </si>
+  <si>
+    <t>現在サブ項目はありません</t>
+  </si>
+  <si>
+    <t>LC_ADD_SHORTCUTS</t>
+  </si>
+  <si>
+    <t>新增子項目</t>
+  </si>
+  <si>
+    <t>新增子项目</t>
+  </si>
+  <si>
+    <t>Add Subitem</t>
+  </si>
+  <si>
+    <t>サブ項目を追加</t>
+  </si>
+  <si>
+    <t>LC_IMG_UPLOAD_TIPS</t>
+  </si>
+  <si>
+    <t>請上傳正確的圖片格式</t>
+  </si>
+  <si>
+    <t>请上传正确的图片格式</t>
+  </si>
+  <si>
+    <t>Please upload a valid image format</t>
+  </si>
+  <si>
+    <t>正しい画像形式をアップロードしてください</t>
+  </si>
+  <si>
+    <t>LC_IMG_LIMIT_TIPS</t>
+  </si>
+  <si>
+    <t>圖片大小不可超過 2MB</t>
+  </si>
+  <si>
+    <t>图片大小不可超过 2MB</t>
+  </si>
+  <si>
+    <t>Image size must not exceed 2MB</t>
+  </si>
+  <si>
+    <t>画像のサイズは2MBを超えてはいけません</t>
+  </si>
+  <si>
+    <t>LC_CATEGORY_DELETE</t>
+  </si>
+  <si>
+    <t>確定要刪除分類 {name} ?</t>
+  </si>
+  <si>
+    <t>确定要删除分类 {name} ?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete the category {name}?</t>
+  </si>
+  <si>
+    <t>カテゴリ {name} を削除してもよろしいですか？</t>
+  </si>
+  <si>
+    <t>LC_IMG_DELETE</t>
+  </si>
+  <si>
+    <t>確定要刪除圖片?</t>
+  </si>
+  <si>
+    <t>确定要删除图片?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete the image?</t>
+  </si>
+  <si>
+    <t>画像を削除してもよろしいですか？</t>
+  </si>
+  <si>
+    <t>LC_SHORTCUT_DELETE</t>
+  </si>
+  <si>
+    <t>確定要刪除快捷選項 {name} ?</t>
+  </si>
+  <si>
+    <t>确定要删除快捷选项 {name} ?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete the shortcut {name}?</t>
+  </si>
+  <si>
+    <t>ショートカット {name} を削除してもよろしいですか？</t>
+  </si>
+  <si>
+    <t>LC_LOGIN</t>
+  </si>
+  <si>
+    <t>登入</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>ログイン</t>
+  </si>
+  <si>
+    <t>LC_EMAIL</t>
+  </si>
+  <si>
+    <t>信箱</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+  </si>
+  <si>
+    <t>LC_TIPS_EMAIL</t>
+  </si>
+  <si>
+    <t>請輸入信箱</t>
+  </si>
+  <si>
+    <t>请输入邮箱</t>
+  </si>
+  <si>
+    <t>Please enter your email</t>
+  </si>
+  <si>
+    <t>メールアドレスを入力してください</t>
+  </si>
+  <si>
+    <t>LC_PASSWORD</t>
+  </si>
+  <si>
+    <t>密碼</t>
+  </si>
+  <si>
+    <t>密码</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>パスワード</t>
+  </si>
+  <si>
+    <t>LC_TIPS_PASSWORD</t>
+  </si>
+  <si>
+    <t>請輸入密碼</t>
+  </si>
+  <si>
+    <t>请输入密码</t>
+  </si>
+  <si>
+    <t>Please enter your password</t>
+  </si>
+  <si>
+    <t>パスワードを入力してください</t>
+  </si>
+  <si>
+    <t>LC_EMAIL_REMEMBER</t>
+  </si>
+  <si>
+    <t>記住信箱</t>
+  </si>
+  <si>
+    <t>记住邮箱</t>
+  </si>
+  <si>
+    <t>Remember email</t>
+  </si>
+  <si>
+    <t>メールアドレスを記憶する</t>
+  </si>
+  <si>
+    <t>LC_FORGOT_PASSWORD</t>
+  </si>
+  <si>
+    <t>忘記密碼</t>
+  </si>
+  <si>
+    <t>忘记密码</t>
+  </si>
+  <si>
+    <t>Forgot password</t>
+  </si>
+  <si>
+    <t>パスワードを忘れた</t>
+  </si>
+  <si>
+    <t>LC_OTHER_LOGIN</t>
+  </si>
+  <si>
+    <t>使用其他方式登入</t>
+  </si>
+  <si>
+    <t>使用其他方式登录</t>
+  </si>
+  <si>
+    <t>Login with other methods</t>
+  </si>
+  <si>
+    <t>他の方法でログイン</t>
+  </si>
+  <si>
+    <t>LC_USE_TEST_ACCOUNT</t>
+  </si>
+  <si>
+    <t>使用測試帳號登入</t>
+  </si>
+  <si>
+    <t>使用测试帐号登录</t>
+  </si>
+  <si>
+    <t>Use test account to log in</t>
+  </si>
+  <si>
+    <t>テストアカウントでログイン</t>
+  </si>
+  <si>
+    <t>LC_NO_ACCOUNT</t>
+  </si>
+  <si>
+    <t>還沒有帳號嗎?</t>
+  </si>
+  <si>
+    <t>还没有帐号吗?</t>
+  </si>
+  <si>
+    <t>Don't have an account?</t>
+  </si>
+  <si>
+    <t>アカウントをお持ちではありませんか？</t>
+  </si>
+  <si>
+    <t>LC_REGISTER</t>
+  </si>
+  <si>
+    <t>註冊帳號</t>
+  </si>
+  <si>
+    <t>注册帐号</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>新規登録</t>
+  </si>
+  <si>
+    <t>LC_PASSWORD_CHECK</t>
+  </si>
+  <si>
+    <t>密碼確認</t>
+  </si>
+  <si>
+    <t>密码确认</t>
+  </si>
+  <si>
+    <t>Confirm password</t>
+  </si>
+  <si>
+    <t>パスワード確認</t>
+  </si>
+  <si>
+    <t>LC_TIPS_PASSWORD_CHECK</t>
+  </si>
+  <si>
+    <t>請輸入密碼確認</t>
+  </si>
+  <si>
+    <t>请输入密码确认</t>
+  </si>
+  <si>
+    <t>Please enter password confirmation</t>
+  </si>
+  <si>
+    <t>確認のためパスワードを入力してください</t>
+  </si>
+  <si>
+    <t>LC_PASSWORD_TIPS</t>
+  </si>
+  <si>
+    <t>密碼至少需有 6 位</t>
+  </si>
+  <si>
+    <t>密码至少需有 6 位</t>
+  </si>
+  <si>
+    <t>Password must be at least 6 characters</t>
+  </si>
+  <si>
+    <t>パスワードは6文字以上必要です</t>
+  </si>
+  <si>
+    <t>LC_MATCH_TIPS</t>
+  </si>
+  <si>
+    <t>密碼與密碼確認不一致</t>
+  </si>
+  <si>
+    <t>密码与密码确认不一致</t>
+  </si>
+  <si>
+    <t>Password and confirmation do not match</t>
+  </si>
+  <si>
+    <t>パスワードが一致しません</t>
+  </si>
+  <si>
+    <t>LC_REGISTER_TIPS</t>
+  </si>
+  <si>
+    <t>僅提供測試用，帳號將於三日後刪除</t>
+  </si>
+  <si>
+    <t>仅提供测试用，帐号将于三日后删除</t>
+  </si>
+  <si>
+    <t>For testing only, account will be deleted in 3 days</t>
+  </si>
+  <si>
+    <t>テスト用アカウントです。3日後に削除されます</t>
+  </si>
+  <si>
+    <t>LC_REGISTER_SUCCESS</t>
+  </si>
+  <si>
+    <t>註冊成功</t>
+  </si>
+  <si>
+    <t>注册成功</t>
+  </si>
+  <si>
+    <t>Registration successful</t>
+  </si>
+  <si>
+    <t>登録成功</t>
+  </si>
+  <si>
+    <t>LC_TO_LOGIN</t>
+  </si>
+  <si>
+    <t>前往登入</t>
+  </si>
+  <si>
+    <t>前往登录</t>
+  </si>
+  <si>
+    <t>Go to login</t>
+  </si>
+  <si>
+    <t>ログインへ</t>
+  </si>
+  <si>
+    <t>LC_TO_LOGIN_TIPS</t>
+  </si>
+  <si>
+    <t>請返回登入頁登入</t>
+  </si>
+  <si>
+    <t>请返回登录页登录</t>
+  </si>
+  <si>
+    <t>Please return to the login page</t>
+  </si>
+  <si>
+    <t>ログインページに戻ってください</t>
+  </si>
+  <si>
+    <t>LC_RESET_PASSWORD</t>
+  </si>
+  <si>
+    <t>重設密碼</t>
+  </si>
+  <si>
+    <t>重设密码</t>
+  </si>
+  <si>
+    <t>Reset password</t>
+  </si>
+  <si>
+    <t>パスワードをリセット</t>
+  </si>
+  <si>
+    <t>LC_RE_LOGIN</t>
+  </si>
+  <si>
+    <t>返回重新登入</t>
+  </si>
+  <si>
+    <t>返回重新登录</t>
+  </si>
+  <si>
+    <t>Return to login</t>
+  </si>
+  <si>
+    <t>ログインに戻る</t>
+  </si>
+  <si>
+    <t>LC_SEND_RESET_EMAIL</t>
+  </si>
+  <si>
+    <t>發送密碼重設郵件</t>
+  </si>
+  <si>
+    <t>发送密码重设邮件</t>
+  </si>
+  <si>
+    <t>Send password reset email</t>
+  </si>
+  <si>
+    <t>パスワードリセットメールを送信</t>
+  </si>
+  <si>
+    <t>LC_IS_SEND_EMAIL</t>
+  </si>
+  <si>
+    <t>已發送郵件至信箱</t>
+  </si>
+  <si>
+    <t>已发送邮件至邮箱</t>
+  </si>
+  <si>
+    <t>Email has been sent</t>
+  </si>
+  <si>
+    <t>メールを送信しました</t>
+  </si>
+  <si>
+    <t>LC_PLEASE_CHECK</t>
+  </si>
+  <si>
+    <t>請至信箱查看重設郵件</t>
+  </si>
+  <si>
+    <t>请至邮箱查看重设邮件</t>
+  </si>
+  <si>
+    <t>Please check your email for the reset link</t>
+  </si>
+  <si>
+    <t>メールを確認してください</t>
+  </si>
+  <si>
+    <t>LC_DELETE_TIPS</t>
+  </si>
+  <si>
+    <t>確定要刪除 {name} ?</t>
+  </si>
+  <si>
+    <t>确定要删除 {name} ?</t>
+  </si>
+  <si>
+    <t>Are you sure you want to delete {name}?</t>
+  </si>
+  <si>
+    <t>{name} を削除してもよろしいですか？</t>
+  </si>
+  <si>
+    <t>LC_DELETE_SUCCESS</t>
+  </si>
+  <si>
+    <t>刪除成功</t>
+  </si>
+  <si>
+    <t>删除成功</t>
+  </si>
+  <si>
+    <t>Successfully deleted</t>
+  </si>
+  <si>
+    <t>削除成功</t>
+  </si>
+  <si>
+    <t>LC_EDIT_SUCCESS</t>
+  </si>
+  <si>
+    <t>修改成功</t>
+  </si>
+  <si>
+    <t>Successfully edited</t>
+  </si>
+  <si>
+    <t>編集成功</t>
+  </si>
+  <si>
+    <t>LC_ADD_SUCCESS</t>
+  </si>
+  <si>
+    <t>新增成功</t>
+  </si>
+  <si>
+    <t>Successfully added</t>
+  </si>
+  <si>
+    <t>追加成功</t>
+  </si>
+  <si>
+    <t>LC_WARN</t>
+  </si>
+  <si>
+    <t>警告</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>LC_SUBMIT</t>
+  </si>
+  <si>
+    <t>送出</t>
+  </si>
+  <si>
+    <t>提交</t>
+  </si>
+  <si>
+    <t>Submit</t>
+  </si>
+  <si>
+    <t>送信</t>
+  </si>
+  <si>
+    <t>LC_CANCEL</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>キャンセル</t>
+  </si>
+  <si>
+    <t>LC_CLOSE</t>
+  </si>
+  <si>
+    <t>關閉</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>閉じる</t>
+  </si>
+  <si>
+    <t>LC_EDIT</t>
+  </si>
+  <si>
+    <t>編輯</t>
+  </si>
+  <si>
+    <t>编辑</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>編集</t>
+  </si>
+  <si>
+    <t>LC_DELETE</t>
+  </si>
+  <si>
+    <t>刪除</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>削除</t>
   </si>
 </sst>
 </file>
@@ -293,6 +1688,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="29.0"/>
+    <col customWidth="1" min="2" max="2" width="35.38"/>
+    <col customWidth="1" min="3" max="3" width="34.5"/>
+    <col customWidth="1" min="4" max="4" width="48.13"/>
+    <col customWidth="1" min="5" max="5" width="43.88"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -328,6 +1730,1715 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/src/locales/moneyGone.xlsx
+++ b/src/locales/moneyGone.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="480">
   <si>
     <t>key</t>
   </si>
@@ -896,6 +896,21 @@
   </si>
   <si>
     <t>画像のサイズは2MBを超えてはいけません</t>
+  </si>
+  <si>
+    <t>LC_IMG_UPLOAD_ERROR</t>
+  </si>
+  <si>
+    <t>圖片上傳失敗</t>
+  </si>
+  <si>
+    <t>图片上传失败</t>
+  </si>
+  <si>
+    <t>Image upload failed</t>
+  </si>
+  <si>
+    <t>画像のアップロードに失敗しました</t>
   </si>
   <si>
     <t>LC_CATEGORY_DELETE</t>
@@ -2820,28 +2835,28 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
+      <c r="A70" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>314</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
@@ -3014,28 +3029,28 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
+      <c r="A82" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
@@ -3157,28 +3172,28 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
+      <c r="A91" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>409</v>
-      </c>
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
@@ -3198,28 +3213,28 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+      <c r="A94" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>419</v>
-      </c>
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
@@ -3256,28 +3271,28 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
+      <c r="A98" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>434</v>
-      </c>
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
@@ -3304,71 +3319,71 @@
         <v>441</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
+      <c r="A103" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>449</v>
-      </c>
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="106">
@@ -3379,21 +3394,21 @@
         <v>457</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>462</v>
@@ -3437,6 +3452,23 @@
       </c>
       <c r="E109" s="1" t="s">
         <v>474</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/src/locales/moneyGone.xlsx
+++ b/src/locales/moneyGone.xlsx
@@ -106,7 +106,7 @@
     <t>剩余</t>
   </si>
   <si>
-    <t>Remaining</t>
+    <t>Left</t>
   </si>
   <si>
     <t>残り</t>
@@ -466,10 +466,10 @@
     <t>月报表</t>
   </si>
   <si>
-    <t>Monthly Report</t>
-  </si>
-  <si>
-    <t>月次レポート</t>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>月次</t>
   </si>
   <si>
     <t>LC_YEAR_REPORT</t>
@@ -481,10 +481,10 @@
     <t>年报表</t>
   </si>
   <si>
-    <t>Yearly Report</t>
-  </si>
-  <si>
-    <t>年次レポート</t>
+    <t>Yearly</t>
+  </si>
+  <si>
+    <t>年次</t>
   </si>
   <si>
     <t>LC_FIRST_HALF</t>
@@ -493,10 +493,10 @@
     <t>上半月</t>
   </si>
   <si>
-    <t>First Half of the Month</t>
-  </si>
-  <si>
-    <t>月の前半</t>
+    <t>1st Half</t>
+  </si>
+  <si>
+    <t>前半</t>
   </si>
   <si>
     <t>LC_SECOND_HALF</t>
@@ -505,10 +505,10 @@
     <t>下半月</t>
   </si>
   <si>
-    <t>Second Half of the Month</t>
-  </si>
-  <si>
-    <t>月の後半</t>
+    <t>2nd Half</t>
+  </si>
+  <si>
+    <t>後半</t>
   </si>
   <si>
     <t>LC_MONTH_TOP</t>

--- a/src/locales/moneyGone.xlsx
+++ b/src/locales/moneyGone.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="485">
   <si>
     <t>key</t>
   </si>
@@ -1451,6 +1451,21 @@
   </si>
   <si>
     <t>削除</t>
+  </si>
+  <si>
+    <t>LC_PREVIEW</t>
+  </si>
+  <si>
+    <t>預覽</t>
+  </si>
+  <si>
+    <t>预览</t>
+  </si>
+  <si>
+    <t>Preview</t>
+  </si>
+  <si>
+    <t>プレビュー</t>
   </si>
 </sst>
 </file>
@@ -3471,6 +3486,23 @@
         <v>479</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/src/locales/moneyGone.xlsx
+++ b/src/locales/moneyGone.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="490">
   <si>
     <t>key</t>
   </si>
@@ -427,6 +427,21 @@
     <t>今月はまだ支出がありません</t>
   </si>
   <si>
+    <t>LC_SEARCH_EMPTY</t>
+  </si>
+  <si>
+    <t>沒有符合搜尋的項目</t>
+  </si>
+  <si>
+    <t>没有符合搜索的项目</t>
+  </si>
+  <si>
+    <t>No matching results</t>
+  </si>
+  <si>
+    <t>一致する項目がありません</t>
+  </si>
+  <si>
     <t>LC_BAR_CHART</t>
   </si>
   <si>
@@ -958,6 +973,21 @@
     <t>ショートカット {name} を削除してもよろしいですか？</t>
   </si>
   <si>
+    <t>LC_PREVIEW</t>
+  </si>
+  <si>
+    <t>預覽</t>
+  </si>
+  <si>
+    <t>预览</t>
+  </si>
+  <si>
+    <t>Preview</t>
+  </si>
+  <si>
+    <t>プレビュー</t>
+  </si>
+  <si>
     <t>LC_LOGIN</t>
   </si>
   <si>
@@ -1451,21 +1481,6 @@
   </si>
   <si>
     <t>削除</t>
-  </si>
-  <si>
-    <t>LC_PREVIEW</t>
-  </si>
-  <si>
-    <t>預覽</t>
-  </si>
-  <si>
-    <t>预览</t>
-  </si>
-  <si>
-    <t>Preview</t>
-  </si>
-  <si>
-    <t>プレビュー</t>
   </si>
 </sst>
 </file>
@@ -2241,28 +2256,28 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
@@ -2323,38 +2338,38 @@
         <v>159</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>168</v>
@@ -2452,28 +2467,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="A46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
@@ -2602,21 +2617,21 @@
         <v>237</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>242</v>
@@ -2867,45 +2882,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
+      <c r="A71" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>324</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
@@ -3061,45 +3076,45 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>379</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
@@ -3204,86 +3219,86 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
+      <c r="A92" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>419</v>
-      </c>
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
     </row>
     <row r="95">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+      <c r="A95" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>429</v>
-      </c>
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
@@ -3303,45 +3318,45 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
+      <c r="A99" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>444</v>
-      </c>
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
@@ -3351,85 +3366,85 @@
         <v>446</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
+      <c r="A104" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>460</v>
-      </c>
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>464</v>
@@ -3437,27 +3452,27 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>472</v>
@@ -3501,6 +3516,23 @@
       </c>
       <c r="E111" s="1" t="s">
         <v>484</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
